--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.496766564081045</v>
+        <v>1.21822456666317</v>
       </c>
       <c r="D2" t="n">
-        <v>6.524245332772487</v>
+        <v>1.060189866575529</v>
       </c>
       <c r="E2" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F2" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.81197840060952</v>
+        <v>10.36944649009905</v>
       </c>
       <c r="D3" t="n">
-        <v>72.91590006461301</v>
+        <v>11.84883376049961</v>
       </c>
       <c r="E3" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F3" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.80555733654943</v>
+        <v>8.743403067189284</v>
       </c>
       <c r="D4" t="n">
-        <v>53.9915157518157</v>
+        <v>8.773621309670052</v>
       </c>
       <c r="E4" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F4" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.47804811749395</v>
+        <v>1.702682819092767</v>
       </c>
       <c r="D5" t="n">
-        <v>10.76914297588045</v>
+        <v>1.749985733580574</v>
       </c>
       <c r="E5" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F5" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.9060741212059</v>
+        <v>9.897237044695959</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18197460053045</v>
+        <v>9.942070872586198</v>
       </c>
       <c r="E6" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F6" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.8765068212371</v>
+        <v>9.567432358451029</v>
       </c>
       <c r="D7" t="n">
-        <v>59.06477350375316</v>
+        <v>9.598025694359889</v>
       </c>
       <c r="E7" t="n">
-        <v>23.94298058121085</v>
+        <v>3.890734344446764</v>
       </c>
       <c r="F7" t="n">
-        <v>25.71256495069036</v>
+        <v>4.178291804487184</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
